--- a/results/feature_selection/induction/wrapper/rP_calc/metrics_global.xlsx
+++ b/results/feature_selection/induction/wrapper/rP_calc/metrics_global.xlsx
@@ -488,7 +488,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>svm_linear</t>
+          <t>tweedie</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -496,38 +496,38 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>t, t_ind_ad, P, Plag1</t>
+          <t>t_ind, t_ind_ad, I, X_calc</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.9404007356847897</v>
+        <v>0.8430004197322118</v>
       </c>
       <c r="E2" t="n">
-        <v>0.03313099161057154</v>
+        <v>0.04817533782040212</v>
       </c>
       <c r="F2" t="n">
-        <v>0.002643651083289848</v>
+        <v>0.006964047546893357</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05141644759500454</v>
+        <v>0.08345086906014434</v>
       </c>
       <c r="H2" t="n">
-        <v>474.8993046737629</v>
+        <v>706.6480437227913</v>
       </c>
       <c r="I2" t="n">
-        <v>0.021730335052866</v>
+        <v>0.0539747073631618</v>
       </c>
       <c r="J2" t="n">
-        <v>-312.5220938833816</v>
+        <v>-260.2176991969513</v>
       </c>
       <c r="K2" t="n">
-        <v>-304.5661576971245</v>
+        <v>-252.2617630106942</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>elasticnet_b</t>
+          <t>poisson</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -535,311 +535,311 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>t_ind, t_ind_ad, P, Plag1, dVdt_calc</t>
+          <t>t, t_ind, t_ind_ad, I, X_calc</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.9257358586550196</v>
+        <v>0.8413698225905765</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03903952901279618</v>
+        <v>0.04741787416000313</v>
       </c>
       <c r="F3" t="n">
-        <v>0.003294142637028199</v>
+        <v>0.007036376122580045</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05739462202182535</v>
+        <v>0.08388310987666137</v>
       </c>
       <c r="H3" t="n">
-        <v>748.6165325655353</v>
+        <v>735.2797896433208</v>
       </c>
       <c r="I3" t="n">
-        <v>0.02708514224941386</v>
+        <v>0.0550145165086331</v>
       </c>
       <c r="J3" t="n">
-        <v>-298.6429046889289</v>
+        <v>-257.6597478196141</v>
       </c>
       <c r="K3" t="n">
-        <v>-288.6979844561075</v>
+        <v>-247.7148275867927</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Ridge_b</t>
+          <t>knn</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>t_ind, t_ind_ad, P, Plag1, V_calc</t>
+          <t>t_ind_ad, V_calc, Xlag1_calc</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.9230943707455883</v>
+        <v>0.7363654665126305</v>
       </c>
       <c r="E4" t="n">
-        <v>0.03753176697040147</v>
+        <v>0.05021307805319666</v>
       </c>
       <c r="F4" t="n">
-        <v>0.00341131140502393</v>
+        <v>0.01169406582538347</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05840643290789064</v>
+        <v>0.1081391040529903</v>
       </c>
       <c r="H4" t="n">
-        <v>639.1157408848048</v>
+        <v>638.5904503188282</v>
       </c>
       <c r="I4" t="n">
-        <v>0.02795960675984026</v>
+        <v>0.0887762061239793</v>
       </c>
       <c r="J4" t="n">
-        <v>-296.7555582096481</v>
+        <v>-234.2283830538613</v>
       </c>
       <c r="K4" t="n">
-        <v>-286.8106379768267</v>
+        <v>-228.2614309141684</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LASSO_b</t>
+          <t>svm_rbf</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>t_ind, t_ind_ad, P, Plag1, dVdt_calc</t>
+          <t>t_ind_ad, V_calc</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.9218750319297138</v>
+        <v>0.6355910358974053</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03935583072236603</v>
+        <v>0.05461863705492803</v>
       </c>
       <c r="F5" t="n">
-        <v>0.003465397750191473</v>
+        <v>0.01616412826197408</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05886762905189467</v>
+        <v>0.1271382250229021</v>
       </c>
       <c r="H5" t="n">
-        <v>729.5610746826131</v>
+        <v>823.5201290764062</v>
       </c>
       <c r="I5" t="n">
-        <v>0.02836326884621991</v>
+        <v>0.1216375790141603</v>
       </c>
       <c r="J5" t="n">
-        <v>-295.9061045538419</v>
+        <v>-218.7478830249408</v>
       </c>
       <c r="K5" t="n">
-        <v>-285.9611843210205</v>
+        <v>-214.7699149318123</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>svm_rbf</t>
+          <t>svm_linear</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>P, Plag1</t>
+          <t>t, t_ind, t_ind_ad, X_calc, V_calc</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.8886485179155252</v>
+        <v>0.5156902122305276</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0390407905955627</v>
+        <v>0.09433035700497684</v>
       </c>
       <c r="F6" t="n">
-        <v>0.004939229865014027</v>
+        <v>0.02148258220626867</v>
       </c>
       <c r="G6" t="n">
-        <v>0.07027965470186964</v>
+        <v>0.1465693767683709</v>
       </c>
       <c r="H6" t="n">
-        <v>220.0876690642991</v>
+        <v>1655.050617987449</v>
       </c>
       <c r="I6" t="n">
-        <v>0.03786290553085225</v>
+        <v>0.1628307438752298</v>
       </c>
       <c r="J6" t="n">
-        <v>-282.7694763161276</v>
+        <v>-197.3876913145941</v>
       </c>
       <c r="K6" t="n">
-        <v>-278.791508222999</v>
+        <v>-187.4427710817727</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>tweedie</t>
+          <t>svm_poly</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>P, I, Plag1, X_calc, V_calc</t>
+          <t>T, FS_calc, V_calc</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.8734393161275825</v>
+        <v>0.4335161670330615</v>
       </c>
       <c r="E7" t="n">
-        <v>0.04273956146027635</v>
+        <v>0.1090606079579623</v>
       </c>
       <c r="F7" t="n">
-        <v>0.005613866091562329</v>
+        <v>0.02512758531328099</v>
       </c>
       <c r="G7" t="n">
-        <v>0.07492573717730329</v>
+        <v>0.1585168297477621</v>
       </c>
       <c r="H7" t="n">
-        <v>756.8807932788997</v>
+        <v>1666.81722401801</v>
       </c>
       <c r="I7" t="n">
-        <v>0.04439791142581888</v>
+        <v>0.1890344596093783</v>
       </c>
       <c r="J7" t="n">
-        <v>-269.855845311489</v>
+        <v>-192.9246070721972</v>
       </c>
       <c r="K7" t="n">
-        <v>-259.9109250786676</v>
+        <v>-186.9576549325043</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>poisson</t>
+          <t>elasticnet_b</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>P, I, Plag1, X_calc, V_calc</t>
+          <t>T, FS_calc, V_calc</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.8215756680174588</v>
+        <v>0.4123115201688951</v>
       </c>
       <c r="E8" t="n">
-        <v>0.04881577687958097</v>
+        <v>0.08435720515457304</v>
       </c>
       <c r="F8" t="n">
-        <v>0.007914387601098818</v>
+        <v>0.02606816215256465</v>
       </c>
       <c r="G8" t="n">
-        <v>0.08896284393553759</v>
+        <v>0.1614563784821295</v>
       </c>
       <c r="H8" t="n">
-        <v>692.6546701777756</v>
+        <v>625.4107869951432</v>
       </c>
       <c r="I8" t="n">
-        <v>0.06156737091553152</v>
+        <v>0.1960542574561268</v>
       </c>
       <c r="J8" t="n">
-        <v>-251.3099398714296</v>
+        <v>-190.9401897087968</v>
       </c>
       <c r="K8" t="n">
-        <v>-241.3650196386082</v>
+        <v>-184.9732375691039</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>rf_b</t>
+          <t>LASSO_b</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>T, FS_calc, V_calc</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.767711142962732</v>
+        <v>0.4105920144110482</v>
       </c>
       <c r="E9" t="n">
-        <v>0.06021459072587493</v>
+        <v>0.08428060909697548</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01030366222802538</v>
+        <v>0.02614443445746112</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1015069565499103</v>
+        <v>0.1616924069258081</v>
       </c>
       <c r="H9" t="n">
-        <v>873.1590556927033</v>
+        <v>627.3910987880342</v>
       </c>
       <c r="I9" t="n">
-        <v>0.07739922067079817</v>
+        <v>0.1966234997969084</v>
       </c>
       <c r="J9" t="n">
-        <v>-245.0638181044245</v>
+        <v>-190.7824228991944</v>
       </c>
       <c r="K9" t="n">
-        <v>-243.0748340578602</v>
+        <v>-184.8154707595016</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>knn</t>
+          <t>Ridge_b</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>t_ind, t_ind_ad, FS_calc, V_calc</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.7393072517262287</v>
+        <v>0.3084514286353393</v>
       </c>
       <c r="E10" t="n">
-        <v>0.06964476722318771</v>
+        <v>0.1072446129710892</v>
       </c>
       <c r="F10" t="n">
-        <v>0.01156357673703493</v>
+        <v>0.03067509558786872</v>
       </c>
       <c r="G10" t="n">
-        <v>0.107534072446992</v>
+        <v>0.1751430717666809</v>
       </c>
       <c r="H10" t="n">
-        <v>1017.313203392419</v>
+        <v>2115.791896191397</v>
       </c>
       <c r="I10" t="n">
-        <v>0.08680232819805585</v>
+        <v>0.2309371383209063</v>
       </c>
       <c r="J10" t="n">
-        <v>-238.8343330929185</v>
+        <v>-180.1524253010182</v>
       </c>
       <c r="K10" t="n">
-        <v>-236.8453490463542</v>
+        <v>-172.1964891147611</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>linear</t>
+          <t>rf_b</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -847,71 +847,71 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>FS_calc</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.718694150039934</v>
+        <v>-0.1022603251536858</v>
       </c>
       <c r="E11" t="n">
-        <v>0.07300454213471216</v>
+        <v>0.09202541944869269</v>
       </c>
       <c r="F11" t="n">
-        <v>0.01247791434218939</v>
+        <v>0.04889308175430411</v>
       </c>
       <c r="G11" t="n">
-        <v>0.1117045851439832</v>
+        <v>0.2211178006274124</v>
       </c>
       <c r="H11" t="n">
-        <v>1200.318379211532</v>
+        <v>628.9512545812836</v>
       </c>
       <c r="I11" t="n">
-        <v>0.09362629502755239</v>
+        <v>0.7308065095482373</v>
       </c>
       <c r="J11" t="n">
-        <v>-234.7249327012872</v>
+        <v>-160.978445976073</v>
       </c>
       <c r="K11" t="n">
-        <v>-232.735948654723</v>
+        <v>-158.9894619295088</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>svm_poly</t>
+          <t>linear</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>P, FS_calc, Plag1</t>
+          <t>FS_calc</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.7109503460050964</v>
+        <v>-0.2288941559918909</v>
       </c>
       <c r="E12" t="n">
-        <v>0.05810840276666883</v>
+        <v>0.1278793907482062</v>
       </c>
       <c r="F12" t="n">
-        <v>0.01282140710440219</v>
+        <v>0.05451019243382513</v>
       </c>
       <c r="G12" t="n">
-        <v>0.1132316523963251</v>
+        <v>0.2334741793728487</v>
       </c>
       <c r="H12" t="n">
-        <v>397.2692886047196</v>
+        <v>1486.730157636367</v>
       </c>
       <c r="I12" t="n">
-        <v>0.09718988117155263</v>
+        <v>0.8146507630024898</v>
       </c>
       <c r="J12" t="n">
-        <v>-229.2585100488621</v>
+        <v>-155.1058491938591</v>
       </c>
       <c r="K12" t="n">
-        <v>-223.2915579091693</v>
+        <v>-153.1168651472948</v>
       </c>
     </row>
   </sheetData>

--- a/results/feature_selection/induction/wrapper/rP_calc/metrics_global.xlsx
+++ b/results/feature_selection/induction/wrapper/rP_calc/metrics_global.xlsx
@@ -488,40 +488,40 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>tweedie</t>
+          <t>knn</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>t_ind, t_ind_ad, I, X_calc</t>
+          <t>t_ind_ad, X_calc, V_calc</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.8430004197322118</v>
+        <v>0.7300151506779873</v>
       </c>
       <c r="E2" t="n">
-        <v>0.04817533782040212</v>
+        <v>0.05265655529969589</v>
       </c>
       <c r="F2" t="n">
-        <v>0.006964047546893357</v>
+        <v>0.01197574747914849</v>
       </c>
       <c r="G2" t="n">
-        <v>0.08345086906014434</v>
+        <v>0.1094337584073054</v>
       </c>
       <c r="H2" t="n">
-        <v>706.6480437227913</v>
+        <v>644.3263718866996</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0539747073631618</v>
+        <v>0.09087847803200777</v>
       </c>
       <c r="J2" t="n">
-        <v>-260.2176991969513</v>
+        <v>-232.9430727537781</v>
       </c>
       <c r="K2" t="n">
-        <v>-252.2617630106942</v>
+        <v>-226.9761206140853</v>
       </c>
     </row>
     <row r="3">
@@ -531,159 +531,159 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>t, t_ind, t_ind_ad, I, X_calc</t>
+          <t>t, t_ind_ad, I, X_calc</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.8413698225905765</v>
+        <v>0.6509990879139222</v>
       </c>
       <c r="E3" t="n">
-        <v>0.04741787416000313</v>
+        <v>0.06868710026436593</v>
       </c>
       <c r="F3" t="n">
-        <v>0.007036376122580045</v>
+        <v>0.01548067161409638</v>
       </c>
       <c r="G3" t="n">
-        <v>0.08388310987666137</v>
+        <v>0.1244213470996693</v>
       </c>
       <c r="H3" t="n">
-        <v>735.2797896433208</v>
+        <v>570.3774680526629</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0550145165086331</v>
+        <v>0.1175367437556908</v>
       </c>
       <c r="J3" t="n">
-        <v>-257.6597478196141</v>
+        <v>-217.0808033952606</v>
       </c>
       <c r="K3" t="n">
-        <v>-247.7148275867927</v>
+        <v>-209.1248672090035</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>knn</t>
+          <t>svm_rbf</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>t_ind_ad, V_calc, Xlag1_calc</t>
+          <t>t_ind_ad, V_calc</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.7363654665126305</v>
+        <v>0.6355910358974053</v>
       </c>
       <c r="E4" t="n">
-        <v>0.05021307805319666</v>
+        <v>0.05461863705492803</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01169406582538347</v>
+        <v>0.01616412826197408</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1081391040529903</v>
+        <v>0.1271382250229021</v>
       </c>
       <c r="H4" t="n">
-        <v>638.5904503188282</v>
+        <v>823.5201290764062</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0887762061239793</v>
+        <v>0.1216375790141603</v>
       </c>
       <c r="J4" t="n">
-        <v>-234.2283830538613</v>
+        <v>-218.7478830249408</v>
       </c>
       <c r="K4" t="n">
-        <v>-228.2614309141684</v>
+        <v>-214.7699149318123</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>svm_rbf</t>
+          <t>tweedie</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>t_ind_ad, V_calc</t>
+          <t>t, t_ind_ad, I, FS_calc</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.6355910358974053</v>
+        <v>0.5684847789121987</v>
       </c>
       <c r="E5" t="n">
-        <v>0.05461863705492803</v>
+        <v>0.07202920012690056</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01616412826197408</v>
+        <v>0.01914076783987559</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1271382250229021</v>
+        <v>0.1383501638592293</v>
       </c>
       <c r="H5" t="n">
-        <v>823.5201290764062</v>
+        <v>1712.537957205178</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1216375790141603</v>
+        <v>0.1448531038142533</v>
       </c>
       <c r="J5" t="n">
-        <v>-218.7478830249408</v>
+        <v>-205.6204779437495</v>
       </c>
       <c r="K5" t="n">
-        <v>-214.7699149318123</v>
+        <v>-197.6645417574924</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>svm_linear</t>
+          <t>svm_poly</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>t, t_ind, t_ind_ad, X_calc, V_calc</t>
+          <t>T, FS_calc, V_calc</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.5156902122305276</v>
+        <v>0.4335161670330615</v>
       </c>
       <c r="E6" t="n">
-        <v>0.09433035700497684</v>
+        <v>0.1090606079579623</v>
       </c>
       <c r="F6" t="n">
-        <v>0.02148258220626867</v>
+        <v>0.02512758531328099</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1465693767683709</v>
+        <v>0.1585168297477621</v>
       </c>
       <c r="H6" t="n">
-        <v>1655.050617987449</v>
+        <v>1666.81722401801</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1628307438752298</v>
+        <v>0.1890344596093783</v>
       </c>
       <c r="J6" t="n">
-        <v>-197.3876913145941</v>
+        <v>-192.9246070721972</v>
       </c>
       <c r="K6" t="n">
-        <v>-187.4427710817727</v>
+        <v>-186.9576549325043</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>svm_poly</t>
+          <t>elasticnet_b</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -695,34 +695,34 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.4335161670330615</v>
+        <v>0.4123115201688951</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1090606079579623</v>
+        <v>0.08435720515457304</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02512758531328099</v>
+        <v>0.02606816215256465</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1585168297477621</v>
+        <v>0.1614563784821295</v>
       </c>
       <c r="H7" t="n">
-        <v>1666.81722401801</v>
+        <v>625.4107869951432</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1890344596093783</v>
+        <v>0.1960542574561268</v>
       </c>
       <c r="J7" t="n">
-        <v>-192.9246070721972</v>
+        <v>-190.9401897087968</v>
       </c>
       <c r="K7" t="n">
-        <v>-186.9576549325043</v>
+        <v>-184.9732375691039</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>elasticnet_b</t>
+          <t>LASSO_b</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -734,67 +734,67 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.4123115201688951</v>
+        <v>0.4105920144110482</v>
       </c>
       <c r="E8" t="n">
-        <v>0.08435720515457304</v>
+        <v>0.08428060909697548</v>
       </c>
       <c r="F8" t="n">
-        <v>0.02606816215256465</v>
+        <v>0.02614443445746112</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1614563784821295</v>
+        <v>0.1616924069258081</v>
       </c>
       <c r="H8" t="n">
-        <v>625.4107869951432</v>
+        <v>627.3910987880342</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1960542574561268</v>
+        <v>0.1966234997969084</v>
       </c>
       <c r="J8" t="n">
-        <v>-190.9401897087968</v>
+        <v>-190.7824228991944</v>
       </c>
       <c r="K8" t="n">
-        <v>-184.9732375691039</v>
+        <v>-184.8154707595016</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>LASSO_b</t>
+          <t>svm_linear</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>T, FS_calc, V_calc</t>
+          <t>V_calc, Xlag1_calc</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.4105920144110482</v>
+        <v>0.3252024687254386</v>
       </c>
       <c r="E9" t="n">
-        <v>0.08428060909697548</v>
+        <v>0.09470726893096</v>
       </c>
       <c r="F9" t="n">
-        <v>0.02614443445746112</v>
+        <v>0.0299320678711806</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1616924069258081</v>
+        <v>0.1730088664525047</v>
       </c>
       <c r="H9" t="n">
-        <v>627.3910987880342</v>
+        <v>620.3902041708174</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1966234997969084</v>
+        <v>0.2243917068921949</v>
       </c>
       <c r="J9" t="n">
-        <v>-190.7824228991944</v>
+        <v>-185.4765429397276</v>
       </c>
       <c r="K9" t="n">
-        <v>-184.8154707595016</v>
+        <v>-181.498574846599</v>
       </c>
     </row>
     <row r="10">
@@ -808,32 +808,32 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>t_ind, t_ind_ad, FS_calc, V_calc</t>
+          <t>t, t_ind_ad, FS_calc, V_calc</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.3084514286353393</v>
+        <v>0.2731421147013229</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1072446129710892</v>
+        <v>0.1099721068297573</v>
       </c>
       <c r="F10" t="n">
-        <v>0.03067509558786872</v>
+        <v>0.03224131468645013</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1751430717666809</v>
+        <v>0.1795586664197808</v>
       </c>
       <c r="H10" t="n">
-        <v>2115.791896191397</v>
+        <v>2286.405912600383</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2309371383209063</v>
+        <v>0.2426262858701183</v>
       </c>
       <c r="J10" t="n">
-        <v>-180.1524253010182</v>
+        <v>-177.4633555392085</v>
       </c>
       <c r="K10" t="n">
-        <v>-172.1964891147611</v>
+        <v>-169.5074193529514</v>
       </c>
     </row>
     <row r="11">
